--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -841,20 +841,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Sirjana kumari chand</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841124691</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841124691</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +863,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9841124691</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9841124691</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +881,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.7499</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.7499</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +938,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33821</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33821</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1015,7 +1001,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1306,7 +1292,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,14 +494,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,30 +511,30 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="27" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,6 +978,205 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 9:05 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375053</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Lal Bahadur majhi</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Lal Bahadur majhi</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9808883377</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:05:03 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9808883377</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 05:35:08 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:05:03 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Chyasal Sramik Shanti school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>02:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB117</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>15h 29m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -992,16 +1191,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1029,7 +1228,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1039,7 +1238,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1074,7 +1273,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>14h 45m</t>
+          <t>15h 7m</t>
         </is>
       </c>
     </row>
@@ -1126,203 +1325,311 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1375001</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Sirjana kumari chand</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>20 Oct 2026 06:39:31 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 03:53:33 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>20 Oct 2026 06:39:31 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>14h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1375053</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Lal Bahadur majhi</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:05:03 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 05:35:08 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:05:03 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>15h 29m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1048,10 +1048,8 @@
           <t>Lal Bahadur majhi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9808883377</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9808883377</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1066,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9808883377</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9808883377</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1137,10 +1133,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1151,7 +1145,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1200,7 +1194,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1599,7 +1593,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,14 +494,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -510,15 +510,15 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1171,6 +1171,838 @@
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 9:50 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374322</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9862297207</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:50:31 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9841168136</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 02:51:10 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:50:31 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.648692</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Nakhipot Basket Ball court,Bishal Chowk - Nakhipot Rd, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>yalung3695@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.317467</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 59m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 9:48 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>for wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375027</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Chaudhary</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Chaudhary</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9803256633</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:48:41 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9803256633</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 04:43:30 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:48:41 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.67027</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Ekantakuna Near DAV sushil kedia vishwa bharti school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>03:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.30694</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>17h 5m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 9:47 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>iptv related issue</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374997</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Sapkota</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Sapkota</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9841509605</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 04:02:45 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841509605</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:41:09 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:47:53 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.672256</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Near Global Pathshala (Pre-school Block) M9FF+55J, Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>pramodsapkota26@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.373051</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>17h 45m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>18h 6m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 9:45 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : skycom iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>skycom iptv issue</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374937</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Suman Ghimire</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Suman Ghimire</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9862428157</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:45:09 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9862428157</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:37:02 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:45:09 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.70804</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near HEMS School, Ratopul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>suman@seedinnovations.com.np</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L6-3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.33906</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : skycom iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>19h 8m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : skycom iptv issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1185,16 +2017,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1222,7 +2054,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1232,7 +2064,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +2075,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1267,7 +2099,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 7m</t>
+          <t>15h 47m</t>
         </is>
       </c>
     </row>
@@ -1308,10 +2140,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1322,308 +2154,457 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Slow Internet Connection</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Video content is Buffering</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>TKT1375001</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Sirjana kumari chand</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>20 Oct 2026 06:39:31 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 03:53:33 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>20 Oct 2026 06:39:31 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>14h 45m</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TKT1375053</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Lal Bahadur majhi</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : slow internet   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>20 Oct 2026 09:05:03 AM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>19 Oct 2026 05:35:08 PM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>20 Oct 2026 09:05:03 AM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>15h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375027</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Chaudhary</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:48:41 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 04:43:30 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:48:41 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>17h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1241,10 +1241,8 @@
           <t>Badri Kuamar Rai</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9862297207</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9862297207</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1259,10 +1257,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9841168136</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9841168136</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1279,10 +1275,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.648692</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.648692</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1334,25 +1328,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>3,7</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.317467</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.31746699999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue    has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1448,10 +1438,8 @@
           <t>Sabina Chaudhary</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9803256633</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9803256633</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1466,10 +1454,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9803256633</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9803256633</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1486,10 +1472,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.67027</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.67027</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1541,25 +1525,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.30694</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.30694</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1645,20 +1625,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Pramod Sapkota</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9841509605</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9841509605</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1673,10 +1647,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9841509605</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9841509605</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1693,10 +1665,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.672256</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.672256</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1748,25 +1718,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.373051</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.373051</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1862,10 +1828,8 @@
           <t>Suman Ghimire</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9862428157</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9862428157</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1880,10 +1844,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9862428157</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9862428157</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1900,10 +1862,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.70804</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.70804</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1941,10 +1901,8 @@
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH7" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI7" s="3" t="inlineStr"/>
       <c r="AJ7" s="3" t="inlineStr"/>
@@ -1959,25 +1917,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L6-3</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.33906</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.33906</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : skycom iptv issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2026,7 +1980,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2574,7 +2528,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1957,6 +1957,217 @@
       <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 12:19 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>ssid not shown</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375113</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>kalapa ghinere</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>kalapa ghinere</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9869540346</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:35:25 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>KLK9869540346</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:04:04 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 12:19:34 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>kalanki kalika petrol pump , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>bdc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>02:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>15h 44m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>16h 15m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1971,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1980,7 +2191,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2008,7 +2219,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2018,7 +2229,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2029,7 +2240,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2252,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 56m</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2264,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 47m</t>
+          <t>15h 54m</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2355,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -2159,100 +2370,95 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -2266,299 +2472,412 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1375001</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Sirjana kumari chand</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>20 Oct 2026 06:39:31 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 03:53:33 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>20 Oct 2026 06:39:31 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>14h 45m</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1375053</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Lal Bahadur majhi</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Slow Internet Connection</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Video content is Buffering</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>20 Oct 2026 09:05:03 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>19 Oct 2026 05:35:08 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>20 Oct 2026 09:05:03 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>15h 29m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>TKT1375001</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana kumari chand</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 06:39:31 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 03:53:33 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 06:39:31 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>14h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1375053</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Lal Bahadur majhi</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:05:03 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 05:35:08 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 09:05:03 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>15h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>TKT1375027</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Sabina Chaudhary</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Case : for wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>20 Oct 2026 09:48:41 AM</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>19 Oct 2026 04:43:30 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>20 Oct 2026 09:48:41 AM</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>17h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1375113</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>kalapa ghinere</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:35:25 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 08:04:04 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 12:19:34 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>15h 44m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>16h 15m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2027,10 +2027,8 @@
           <t>kalapa ghinere</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9869540346</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9869540346</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2065,10 +2063,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2124,25 +2120,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : ssid not shown  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2191,7 +2183,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2847,7 +2839,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : ssid not shown  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -513,7 +513,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -2160,6 +2160,404 @@
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 3:08 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374369</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Leela Bahad Neupane</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Leela Bahad Neupane</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841316684</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 03:28:22 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841316684</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:01:15 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 03:28:22 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>near by Balaju bypass - Clothing store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9841316684@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB081</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 27m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 3:07 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374369</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Leela Bahad Neupane</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Leela Bahad Neupane</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841316684</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 03:28:22 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841316684</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 04:01:15 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 03:28:22 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>near by Balaju bypass - Clothing store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>9841316684@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB081</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 27m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2609,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2232,7 +2630,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -2297,14 +2695,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2427,14 +2825,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2230,10 +2230,8 @@
           <t>Leela Bahad Neupane</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841316684</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841316684</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2319,10 +2317,8 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2329,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2429,10 +2425,8 @@
           <t>Leela Bahad Neupane</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841316684</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841316684</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2518,10 +2512,8 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2532,7 +2524,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
